--- a/Proyecto/data/PowerFlow_Results_Study1/res_line/loading_percent.xlsx
+++ b/Proyecto/data/PowerFlow_Results_Study1/res_line/loading_percent.xlsx
@@ -394,22 +394,22 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>23.68936966559923</v>
+        <v>23.6893696655993</v>
       </c>
       <c r="C2">
-        <v>0.7136606511504764</v>
+        <v>0.7136606511504713</v>
       </c>
       <c r="D2">
-        <v>36.61813820766451</v>
+        <v>36.61813820766459</v>
       </c>
       <c r="E2">
-        <v>63.17777070630382</v>
+        <v>63.17777070630384</v>
       </c>
       <c r="F2">
-        <v>52.03594044852663</v>
+        <v>52.03594044852664</v>
       </c>
       <c r="G2">
-        <v>24.13037789001119</v>
+        <v>24.13037789001116</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -417,22 +417,22 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>23.12172441662437</v>
+        <v>23.12172441662436</v>
       </c>
       <c r="C3">
-        <v>0.7144311633088212</v>
+        <v>0.7144311633088855</v>
       </c>
       <c r="D3">
-        <v>37.69323787726501</v>
+        <v>37.69323787726469</v>
       </c>
       <c r="E3">
-        <v>63.11429462540749</v>
+        <v>63.11429462540743</v>
       </c>
       <c r="F3">
-        <v>52.23219352931786</v>
+        <v>52.23219352931776</v>
       </c>
       <c r="G3">
-        <v>24.86158011200884</v>
+        <v>24.86158011200875</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -440,22 +440,22 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>22.76621310442584</v>
+        <v>22.76621310442585</v>
       </c>
       <c r="C4">
         <v>0.714898344186247</v>
       </c>
       <c r="D4">
-        <v>38.43425781708205</v>
+        <v>38.43425781708216</v>
       </c>
       <c r="E4">
-        <v>63.08260310991761</v>
+        <v>63.08260310991759</v>
       </c>
       <c r="F4">
-        <v>52.36341477571828</v>
+        <v>52.36341477571832</v>
       </c>
       <c r="G4">
-        <v>25.33347255671802</v>
+        <v>25.33347255671811</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -463,22 +463,22 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>22.50434004589641</v>
+        <v>22.50434004589636</v>
       </c>
       <c r="C5">
         <v>0.7152155513837313</v>
       </c>
       <c r="D5">
-        <v>39.05085871960479</v>
+        <v>39.05085871960465</v>
       </c>
       <c r="E5">
-        <v>63.08620484059838</v>
+        <v>63.08620484059843</v>
       </c>
       <c r="F5">
-        <v>52.48721168276388</v>
+        <v>52.48721168276391</v>
       </c>
       <c r="G5">
-        <v>25.71019394524042</v>
+        <v>25.71019394524039</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -486,22 +486,22 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>22.93552724226891</v>
+        <v>22.93552724226893</v>
       </c>
       <c r="C6">
-        <v>0.7146430183934617</v>
+        <v>0.7146430183933922</v>
       </c>
       <c r="D6">
-        <v>38.14248542751164</v>
+        <v>38.14248542751167</v>
       </c>
       <c r="E6">
-        <v>63.13838190181151</v>
+        <v>63.1383819018115</v>
       </c>
       <c r="F6">
         <v>52.341728316376</v>
       </c>
       <c r="G6">
-        <v>25.14763762742247</v>
+        <v>25.14763762742246</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -509,22 +509,22 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>23.4168781126409</v>
+        <v>23.41687811264086</v>
       </c>
       <c r="C7">
-        <v>0.7139873396116967</v>
+        <v>0.713987339611702</v>
       </c>
       <c r="D7">
-        <v>37.20772853511632</v>
+        <v>37.20772853511625</v>
       </c>
       <c r="E7">
-        <v>63.20268019946433</v>
+        <v>63.20268019946439</v>
       </c>
       <c r="F7">
-        <v>52.18568429107853</v>
+        <v>52.18568429107867</v>
       </c>
       <c r="G7">
-        <v>24.53338690044072</v>
+        <v>24.53338690044077</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -532,22 +532,22 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>23.69990861297136</v>
+        <v>23.69990861297137</v>
       </c>
       <c r="C8">
-        <v>0.7135683031604259</v>
+        <v>0.7135683031602263</v>
       </c>
       <c r="D8">
-        <v>36.74698436935143</v>
+        <v>36.74698436935124</v>
       </c>
       <c r="E8">
-        <v>63.2747581600142</v>
+        <v>63.27475816001428</v>
       </c>
       <c r="F8">
-        <v>52.12848514326704</v>
+        <v>52.12848514326714</v>
       </c>
       <c r="G8">
-        <v>24.20933149066078</v>
+        <v>24.20933149066081</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -558,19 +558,19 @@
         <v>24.65070765032772</v>
       </c>
       <c r="C9">
-        <v>0.7121912001131337</v>
+        <v>0.7121912001131371</v>
       </c>
       <c r="D9">
-        <v>35.28660097769048</v>
+        <v>35.2866009776906</v>
       </c>
       <c r="E9">
-        <v>63.44384794078605</v>
+        <v>63.44384794078611</v>
       </c>
       <c r="F9">
-        <v>51.86387694885764</v>
+        <v>51.8638769488576</v>
       </c>
       <c r="G9">
-        <v>23.07318599404469</v>
+        <v>23.07318599404466</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -581,10 +581,10 @@
         <v>25.55544040635863</v>
       </c>
       <c r="C10">
-        <v>0.7108705390828103</v>
+        <v>0.7108705390828088</v>
       </c>
       <c r="D10">
-        <v>34.15898487519172</v>
+        <v>34.15898487519182</v>
       </c>
       <c r="E10">
         <v>63.56477745114311</v>
@@ -593,7 +593,7 @@
         <v>51.5732243423192</v>
       </c>
       <c r="G10">
-        <v>21.99034975380136</v>
+        <v>21.99034975380133</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -604,19 +604,19 @@
         <v>25.92164432802332</v>
       </c>
       <c r="C11">
-        <v>0.7103219779302511</v>
+        <v>0.7103219779303171</v>
       </c>
       <c r="D11">
-        <v>33.80243326385906</v>
+        <v>33.80243326385845</v>
       </c>
       <c r="E11">
-        <v>63.61664523012922</v>
+        <v>63.61664523012912</v>
       </c>
       <c r="F11">
-        <v>51.45888132134601</v>
+        <v>51.45888132134587</v>
       </c>
       <c r="G11">
-        <v>21.56602580205067</v>
+        <v>21.56602580205045</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -624,22 +624,22 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>26.04495230883805</v>
+        <v>26.04495230883814</v>
       </c>
       <c r="C12">
-        <v>0.7101515563603434</v>
+        <v>0.7101515563603419</v>
       </c>
       <c r="D12">
-        <v>33.670853118409</v>
+        <v>33.67085311840913</v>
       </c>
       <c r="E12">
-        <v>63.6135728477059</v>
+        <v>63.61357284770598</v>
       </c>
       <c r="F12">
-        <v>51.39978588736371</v>
+        <v>51.39978588736377</v>
       </c>
       <c r="G12">
-        <v>21.40541972261468</v>
+        <v>21.40541972261473</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -647,10 +647,10 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>26.58900385425849</v>
+        <v>26.58900385425844</v>
       </c>
       <c r="C13">
-        <v>0.7093671302226575</v>
+        <v>0.7093671302226576</v>
       </c>
       <c r="D13">
         <v>33.21284459057859</v>
@@ -659,10 +659,10 @@
         <v>63.62938573717384</v>
       </c>
       <c r="F13">
-        <v>51.16897130063847</v>
+        <v>51.16897130063852</v>
       </c>
       <c r="G13">
-        <v>20.7347814611097</v>
+        <v>20.73478146110967</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -673,19 +673,19 @@
         <v>26.38421479189007</v>
       </c>
       <c r="C14">
-        <v>0.7096854116033948</v>
+        <v>0.7096854116035299</v>
       </c>
       <c r="D14">
-        <v>33.33738076636363</v>
+        <v>33.33738076636347</v>
       </c>
       <c r="E14">
-        <v>63.59566884503748</v>
+        <v>63.59566884503739</v>
       </c>
       <c r="F14">
-        <v>51.22780935761401</v>
+        <v>51.22780935761404</v>
       </c>
       <c r="G14">
-        <v>20.95929900426335</v>
+        <v>20.95929900426324</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -693,22 +693,22 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>25.14801841479088</v>
+        <v>25.14801841479087</v>
       </c>
       <c r="C15">
-        <v>0.7115026901627771</v>
+        <v>0.7115026901625068</v>
       </c>
       <c r="D15">
-        <v>34.57067589438065</v>
+        <v>34.57067589438073</v>
       </c>
       <c r="E15">
-        <v>63.46924292263702</v>
+        <v>63.469242922637</v>
       </c>
       <c r="F15">
-        <v>51.66268499947181</v>
+        <v>51.66268499947194</v>
       </c>
       <c r="G15">
-        <v>22.43422323316967</v>
+        <v>22.4342232331698</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -716,22 +716,22 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>24.61743118696248</v>
+        <v>24.61743118696243</v>
       </c>
       <c r="C16">
-        <v>0.7123011368526234</v>
+        <v>0.7123011368527554</v>
       </c>
       <c r="D16">
-        <v>35.22331897921537</v>
+        <v>35.22331897921538</v>
       </c>
       <c r="E16">
-        <v>63.36132248381112</v>
+        <v>63.36132248381108</v>
       </c>
       <c r="F16">
-        <v>51.79617010729972</v>
+        <v>51.79617010729976</v>
       </c>
       <c r="G16">
-        <v>23.03907887326546</v>
+        <v>23.03907887326545</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -739,22 +739,22 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>25.37084200271055</v>
+        <v>25.37084200271057</v>
       </c>
       <c r="C17">
-        <v>0.7112256624313532</v>
+        <v>0.7112256624311523</v>
       </c>
       <c r="D17">
-        <v>34.22478358291843</v>
+        <v>34.22478358291855</v>
       </c>
       <c r="E17">
-        <v>63.43474094684201</v>
+        <v>63.43474094684207</v>
       </c>
       <c r="F17">
-        <v>51.52655454787586</v>
+        <v>51.52655454787585</v>
       </c>
       <c r="G17">
-        <v>22.10835611818543</v>
+        <v>22.10835611818544</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -762,13 +762,13 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>26.90349988937924</v>
+        <v>26.90349988937926</v>
       </c>
       <c r="C18">
-        <v>0.7089117275939255</v>
+        <v>0.708911727593988</v>
       </c>
       <c r="D18">
-        <v>33.00687142233678</v>
+        <v>33.00687142233667</v>
       </c>
       <c r="E18">
         <v>63.63141799908595</v>
@@ -777,7 +777,7 @@
         <v>51.02916393918244</v>
       </c>
       <c r="G18">
-        <v>20.34864820083795</v>
+        <v>20.34864820083804</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -785,22 +785,22 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>28.7019923773954</v>
+        <v>28.70199237739526</v>
       </c>
       <c r="C19">
-        <v>0.7060294852142653</v>
+        <v>0.7060294852143316</v>
       </c>
       <c r="D19">
-        <v>32.95098387627512</v>
+        <v>32.95098387627458</v>
       </c>
       <c r="E19">
-        <v>63.88810864423663</v>
+        <v>63.88810864423657</v>
       </c>
       <c r="F19">
-        <v>50.47962549559135</v>
+        <v>50.47962549559121</v>
       </c>
       <c r="G19">
-        <v>18.48902843343444</v>
+        <v>18.48902843343425</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -808,22 +808,22 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>30.72118283669239</v>
+        <v>30.72118283669235</v>
       </c>
       <c r="C20">
-        <v>0.7025774150428425</v>
+        <v>0.7025774150428417</v>
       </c>
       <c r="D20">
-        <v>34.57081463975892</v>
+        <v>34.57081463975904</v>
       </c>
       <c r="E20">
-        <v>64.22353311374945</v>
+        <v>64.22353311374937</v>
       </c>
       <c r="F20">
-        <v>49.91857885552478</v>
+        <v>49.91857885552475</v>
       </c>
       <c r="G20">
-        <v>16.73669921211205</v>
+        <v>16.73669921211207</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -831,22 +831,22 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>32.43729451761887</v>
+        <v>32.43729451761882</v>
       </c>
       <c r="C21">
-        <v>0.6994977796889181</v>
+        <v>0.6994977796889182</v>
       </c>
       <c r="D21">
-        <v>37.1119275366237</v>
+        <v>37.11192753662334</v>
       </c>
       <c r="E21">
-        <v>64.50775728525207</v>
+        <v>64.50775728525204</v>
       </c>
       <c r="F21">
-        <v>49.44899833015581</v>
+        <v>49.4489983301558</v>
       </c>
       <c r="G21">
-        <v>15.55401471090855</v>
+        <v>15.55401471090851</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -854,22 +854,22 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>30.67674238499395</v>
+        <v>30.67674238499401</v>
       </c>
       <c r="C22">
-        <v>0.7026369678008362</v>
+        <v>0.7026369678009018</v>
       </c>
       <c r="D22">
-        <v>34.52340331569476</v>
+        <v>34.5234033156946</v>
       </c>
       <c r="E22">
-        <v>64.24327074821628</v>
+        <v>64.24327074821626</v>
       </c>
       <c r="F22">
-        <v>49.95812444137383</v>
+        <v>49.95812444137394</v>
       </c>
       <c r="G22">
-        <v>16.79341955656762</v>
+        <v>16.79341955656768</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -877,22 +877,22 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>28.14442257852997</v>
+        <v>28.14442257852996</v>
       </c>
       <c r="C23">
-        <v>0.7069117699610478</v>
+        <v>0.7069117699609815</v>
       </c>
       <c r="D23">
-        <v>32.84111003152063</v>
+        <v>32.8411100315205</v>
       </c>
       <c r="E23">
-        <v>63.84704767882573</v>
+        <v>63.84704767882574</v>
       </c>
       <c r="F23">
-        <v>50.68802734122579</v>
+        <v>50.68802734122585</v>
       </c>
       <c r="G23">
-        <v>19.07646243769395</v>
+        <v>19.07646243769396</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -900,22 +900,22 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>26.14049370827623</v>
+        <v>26.14049370827621</v>
       </c>
       <c r="C24">
-        <v>0.7100435316874372</v>
+        <v>0.7100435316875695</v>
       </c>
       <c r="D24">
-        <v>33.53662010539365</v>
+        <v>33.53662010539334</v>
       </c>
       <c r="E24">
         <v>63.57906907207857</v>
       </c>
       <c r="F24">
-        <v>51.32172151992195</v>
+        <v>51.32172151992188</v>
       </c>
       <c r="G24">
-        <v>21.25149802789679</v>
+        <v>21.25149802789661</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -923,22 +923,22 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>24.63537710976646</v>
+        <v>24.63537710976645</v>
       </c>
       <c r="C25">
-        <v>0.7155632152027789</v>
+        <v>0.7155632152028439</v>
       </c>
       <c r="D25">
-        <v>29.69544259294953</v>
+        <v>29.6954425929502</v>
       </c>
       <c r="E25">
-        <v>58.94478736774079</v>
+        <v>58.9447873677409</v>
       </c>
       <c r="F25">
-        <v>47.34976722406966</v>
+        <v>47.34976722406973</v>
       </c>
       <c r="G25">
-        <v>18.84560194655413</v>
+        <v>18.84560194655435</v>
       </c>
     </row>
   </sheetData>
